--- a/common/template/document/teachers_schedule.xlsx
+++ b/common/template/document/teachers_schedule.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Shared/domains/ais-dsi.loc/common/template/document/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OSPanel\domains\ais-dsi-2.loc\common\template\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D1D36C-7101-2142-951B-DEFC44714C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="460" windowWidth="25440" windowHeight="14260" xr2:uid="{F29247BA-6688-2146-B7E5-FBC3C6D6EF13}"/>
+    <workbookView xWindow="75" yWindow="465" windowWidth="25440" windowHeight="14265"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="152511" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Время</t>
   </si>
@@ -77,34 +76,66 @@
     <t>Расписание занятий преподавателя  [doc.teachers_fio] за  [doc.plan_year] учебный год</t>
   </si>
   <si>
-    <t>Тип</t>
-  </si>
-  <si>
     <t>[day_sub1.subject_type]</t>
   </si>
   <si>
     <t>Согласовано:</t>
   </si>
   <si>
-    <t>Нагр.</t>
-  </si>
-  <si>
-    <t>Деят-ть</t>
-  </si>
-  <si>
     <t xml:space="preserve">[doc.signer_fio] </t>
   </si>
   <si>
     <t>[doc.date_sign]</t>
+  </si>
+  <si>
+    <t>Деятельность:</t>
+  </si>
+  <si>
+    <t>Вид деятельности:</t>
+  </si>
+  <si>
+    <t>Тип занятий:</t>
+  </si>
+  <si>
+    <t>[doc.direction]</t>
+  </si>
+  <si>
+    <t>[doc.direction_vid]</t>
+  </si>
+  <si>
+    <t>[doc.subject_type]</t>
+  </si>
+  <si>
+    <t>[day_sub1.direction_vid]</t>
+  </si>
+  <si>
+    <t>Деятельность</t>
+  </si>
+  <si>
+    <t>Вид деятельности</t>
+  </si>
+  <si>
+    <t>Тип занятий</t>
+  </si>
+  <si>
+    <t>Нагрузка</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -229,36 +260,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -573,115 +616,182 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF30FC6-1D40-1445-AEAF-DBC43CD70656}">
-  <dimension ref="A3:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:H15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" customWidth="1"/>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="8.25" customWidth="1"/>
+    <col min="4" max="4" width="30.375" customWidth="1"/>
     <col min="5" max="5" width="48" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="13.5" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8" t="s">
+    <row r="9" spans="1:8" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" spans="1:7" s="3" customFormat="1" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" s="2" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B10" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G11" s="10" t="s">
-        <v>20</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:G3"/>
+  <mergeCells count="5">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>